--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,10 +521,90 @@
       <c r="C11" t="str">
         <v>595_玉兰叶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>315_尤加利叶圆叶_Eucalyptus Populus_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>462_五针松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>348_万年青_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>431_小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>820_蝴蝶洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>480_蝴蝶洋牡丹红_butterfly  Ranunculus_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -579,7 +659,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202255558550</v>
+        <v>02022555585558510155155530</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -601,6 +601,9 @@
       <c r="C21" t="str">
         <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F21" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -659,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02022555585558510155155530</v>
+        <v>02022555585558510155155533</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -605,9 +605,95 @@
         <v>3</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>707_永生吊米白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4</v>
+      </c>
+      <c r="C24" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F24" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>5</v>
+      </c>
+      <c r="C25" t="str">
+        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>682_锦鲤粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -662,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02022555585558510155155533</v>
+        <v>020225555855585101551555333023335556050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -690,6 +690,9 @@
       <c r="C31" t="str">
         <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -748,7 +751,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020225555855585101551555333023335556050</v>
+        <v>020225555855585101551555333023335556055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,9 +694,92 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>855_海芋粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6</v>
+      </c>
+      <c r="C35" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>191_朱小姐_Miss Piggy_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F39" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>7</v>
+      </c>
+      <c r="C40" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -751,7 +834,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020225555855585101551555333023335556055</v>
+        <v>0202255558555851015515553330233355560555256830108160</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -774,7 +774,7 @@
     </row>
     <row r="41">
       <c r="C41" t="str">
-        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -776,6 +776,9 @@
       <c r="C41" t="str">
         <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -834,7 +837,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202255558555851015515553330233355560555256830108160</v>
+        <v>02022555585558510155155533302333555605552568301081626</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -780,9 +780,95 @@
         <v>26</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>8</v>
+      </c>
+      <c r="C44" t="str">
+        <v>191_朱小姐_Miss Piggy_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>173_朱丽叶_Juliet_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>9</v>
+      </c>
+      <c r="C50" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -837,7 +923,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02022555585558510155155533302333555605552568301081626</v>
+        <v>0202255558555851015515553330233355560555256830108162645111985103610</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -866,9 +866,95 @@
         <v>10</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>10</v>
+      </c>
+      <c r="C52" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>264_和弦_harmony_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>11</v>
+      </c>
+      <c r="C56" t="str">
+        <v>264_和弦_harmony_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>12</v>
+      </c>
+      <c r="C60" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F60" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -923,7 +1009,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202255558555851015515553330233355560555256830108162645111985103610</v>
+        <v>020225555855585101551555333023335556055525683010816264511198510361019185102352020450</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -951,6 +951,9 @@
       <c r="C61" t="str">
         <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
       </c>
+      <c r="F61" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1009,7 +1012,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020225555855585101551555333023335556055525683010816264511198510361019185102352020450</v>
+        <v>0202255558555851015515553330233355560555256830108162645111985103610191851023520204520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -955,9 +955,92 @@
         <v>20</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>45_拉丝艳粉_Spider pink+_Gerbera L._20stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F63" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>327_文竹_asparagus fern_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>13</v>
+      </c>
+      <c r="C66" t="str">
+        <v>452_粉吊鸟_pink hanging heliconia_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>733_芍药弗莱明_Fleming_undefined_10stems</v>
+      </c>
+      <c r="F67" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>645_蛇目菊_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>406_千鸟飞燕 白_larkspur white_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1012,7 +1095,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202255558555851015515553330233355560555256830108162645111985103610191851023520204520</v>
+        <v>02022555585558510155155533302333555605552568301081626451119851036101918510235202045205355515100101550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L81"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1037,10 +1037,101 @@
       <c r="C71" t="str">
         <v>500_千鸟飞燕 粉_larkspur pink_undefined_1bunch</v>
       </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2</v>
+      </c>
+      <c r="C72" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F72" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F73" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>3</v>
+      </c>
+      <c r="C74" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="C75" t="str" xml:space="preserve">
+        <v xml:space="preserve">413_风铃花淡紫色_Canterbury Bells
+light purple_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="C76" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>4</v>
+      </c>
+      <c r="C77" t="str">
+        <v>686_百合小粉仙_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F77" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>191_朱小姐_Miss Piggy_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>260_凯拉_Kayla_Rosa rugosa Thunb._10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1095,7 +1186,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02022555585558510155155533302333555605552568301081626451119851036101918510235202045205355515100101550</v>
+        <v>020225555855585101551555333023335556055525683010816264511198510361019185102352020452053555151001015555520510781050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -1128,6 +1128,9 @@
       <c r="C81" t="str">
         <v>260_凯拉_Kayla_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F81" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1186,7 +1189,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020225555855585101551555333023335556055525683010816264511198510361019185102352020452053555151001015555520510781050</v>
+        <v>020225555855585101551555333023335556055525683010816264511198510361019185102352020452053555151001015555520510781055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1132,9 +1132,97 @@
         <v>5</v>
       </c>
     </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="C83" t="str" xml:space="preserve">
+        <v xml:space="preserve">414_风铃花粉色_Canterbury Bells
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F83" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F84" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F85" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
+        <v>5</v>
+      </c>
+      <c r="C86" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F86" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>8</v>
+      </c>
+      <c r="C87" t="str">
+        <v>377_一叶兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F87" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>9</v>
+      </c>
+      <c r="C88" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F88" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F89" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F90" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1189,7 +1277,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020225555855585101551555333023335556055525683010816264511198510361019185102352020452053555151001015555520510781055</v>
+        <v>02022555585558510155155533302333555605552568301081626451119851036101918510235202045205355515100101555552051078105551010102040105150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-26.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1219,10 +1219,62 @@
       <c r="C91" t="str">
         <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F91" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F92" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>79_福娃_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F93" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>10</v>
+      </c>
+      <c r="C94" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F94" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F95" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>1</v>
+      </c>
+      <c r="C96" t="str">
+        <v>449_柔丽思 绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F96" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1277,7 +1329,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02022555585558510155155533302333555605552568301081626451119851036101918510235202045205355515100101555552051078105551010102040105150</v>
+        <v>02022555585558510155155533302333555605552568301081626451119851036101918510235202045205355515100101555552051078105551010102040105151015940305</v>
       </c>
     </row>
   </sheetData>
